--- a/teams/benefits-portfolio/benefits-intake-optimization/post-go-live/21p-0537/21P-0537 Post-Go-Live Submission Tracker.xlsx
+++ b/teams/benefits-portfolio/benefits-intake-optimization/post-go-live/21p-0537/21P-0537 Post-Go-Live Submission Tracker.xlsx
@@ -1,13 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f465efd6b01b8bba/Documents/GingerHorizonsGroup_Projects/AgileSix/BIO/GH/benefits-intake-optimization/teams/benefits-portfolio/benefits-intake-optimization/post-go-live/21p-0537/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_4E6C840E50AB8BAA97E0FB0AD7083CF2A5308038" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC43CE61-A5F1-45FA-BC37-FEFDBB0D5D02}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="21P-0537" sheetId="1" r:id="rId4"/>
+    <sheet name="21P-0537" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="TyQn9trdjc6Xs9xpemiima9VIxcFN2am7OD965BGFKU="/>
     </ext>
@@ -297,43 +317,43 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color rgb="FF0E2841"/>
       <name val="Play"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0E2841"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF0C0D0E"/>
       <name val="Ui-monospace"/>
     </font>
@@ -343,15 +363,25 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="3">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF45B0E1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -366,69 +396,60 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -618,56 +639,55 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="40.13"/>
-    <col customWidth="1" min="2" max="2" width="36.0"/>
-    <col customWidth="1" min="3" max="3" width="21.38"/>
-    <col customWidth="1" min="4" max="4" width="11.13"/>
-    <col customWidth="1" min="5" max="5" width="15.25"/>
-    <col customWidth="1" min="6" max="6" width="9.38"/>
-    <col customWidth="1" min="7" max="7" width="12.25"/>
-    <col customWidth="1" min="8" max="26" width="8.63"/>
+    <col min="1" max="1" width="40.140625" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="23.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>1921.0</v>
+        <v>1921</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIF(A8:A100000,"&lt;&gt;")</f>
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="C4" s="4">
         <f>B4/B3</f>
-        <v>0.04008328995</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>8.068714211348256E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -676,7 +696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -696,1550 +716,1550 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="8">
-        <v>46066.0</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="s">
+      <c r="C8" s="7">
+        <v>46066</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="11">
-        <v>46065.0</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="10">
+        <v>46065</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="12">
-        <v>6.8908158E7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="s">
+      <c r="E9" s="8"/>
+      <c r="F9" s="11">
+        <v>68908158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="11">
-        <v>46065.0</v>
+      <c r="C10" s="10">
+        <v>46065</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="13">
-        <v>46066.18541666667</v>
-      </c>
-      <c r="F10" s="12">
-        <v>6.8918564E7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
+      <c r="E10" s="8">
+        <v>46066.185416666667</v>
+      </c>
+      <c r="F10" s="11">
+        <v>68918564</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="8">
-        <v>46065.0</v>
+      <c r="C11" s="7">
+        <v>46065</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="14">
-        <v>46065.67916666667</v>
-      </c>
-      <c r="F11" s="12">
-        <v>6.8923229E7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
+      <c r="E11" s="12">
+        <v>46065.679166666669</v>
+      </c>
+      <c r="F11" s="11">
+        <v>68923229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="11">
-        <v>46064.0</v>
+      <c r="C12" s="10">
+        <v>46064</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="8">
         <v>46065.54791666667</v>
       </c>
-      <c r="F12" s="12">
-        <v>6.8899814E7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="s">
+      <c r="F12" s="11">
+        <v>68899814</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="11">
-        <v>46064.0</v>
+      <c r="C13" s="10">
+        <v>46064</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="8">
         <v>46065.493055555555</v>
       </c>
-      <c r="F13" s="12">
-        <v>6.8888958E7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="s">
+      <c r="F13" s="11">
+        <v>68888958</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="8">
-        <v>46064.0</v>
+      <c r="C14" s="7">
+        <v>46064</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="14">
-        <v>46065.31180555555</v>
-      </c>
-      <c r="F14" s="12">
-        <v>6.8865676E7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
+      <c r="E14" s="12">
+        <v>46065.311805555553</v>
+      </c>
+      <c r="F14" s="11">
+        <v>68865676</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="8">
-        <v>46064.0</v>
+      <c r="C15" s="7">
+        <v>46064</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="14">
-        <v>46065.36597222222</v>
-      </c>
-      <c r="F15" s="12">
-        <v>6.8870849E7</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="s">
+      <c r="E15" s="12">
+        <v>46065.365972222222</v>
+      </c>
+      <c r="F15" s="11">
+        <v>68870849</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="11">
-        <v>46063.0</v>
+      <c r="C16" s="10">
+        <v>46063</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="13">
-        <v>46064.45277777778</v>
-      </c>
-      <c r="F16" s="12">
-        <v>6.886125E7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="s">
+      <c r="E16" s="8">
+        <v>46064.452777777777</v>
+      </c>
+      <c r="F16" s="11">
+        <v>68861250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="11">
-        <v>46063.0</v>
+      <c r="C17" s="10">
+        <v>46063</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="8">
         <v>46064.36041666667</v>
       </c>
-      <c r="F17" s="12">
-        <v>6.883051E7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="s">
+      <c r="F17" s="11">
+        <v>68830510</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="8">
-        <v>46063.0</v>
+      <c r="C18" s="7">
+        <v>46063</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="14">
-        <v>46064.45277777778</v>
-      </c>
-      <c r="F18" s="12">
-        <v>6.8852205E7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="s">
+      <c r="E18" s="12">
+        <v>46064.452777777777</v>
+      </c>
+      <c r="F18" s="11">
+        <v>68852205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="11">
-        <v>46062.0</v>
+      <c r="C19" s="10">
+        <v>46062</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="13">
-        <v>46063.39791666667</v>
-      </c>
-      <c r="F19" s="12">
-        <v>6.8814488E7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="s">
+      <c r="E19" s="8">
+        <v>46063.397916666669</v>
+      </c>
+      <c r="F19" s="11">
+        <v>68814488</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="11">
-        <v>46062.0</v>
+      <c r="C20" s="10">
+        <v>46062</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="8">
         <v>46062.615277777775</v>
       </c>
-      <c r="F20" s="12">
-        <v>6.8780835E7</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6" t="s">
+      <c r="F20" s="11">
+        <v>68780835</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="11">
-        <v>46062.0</v>
+      <c r="C21" s="10">
+        <v>46062</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="8">
         <v>46062.615277777775</v>
       </c>
-      <c r="F21" s="12">
-        <v>6.8776068E7</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6" t="s">
+      <c r="F21" s="11">
+        <v>68776068</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="8">
-        <v>46062.0</v>
+      <c r="C22" s="7">
+        <v>46062</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="12">
         <v>46063.399305555555</v>
       </c>
-      <c r="F22" s="12">
-        <v>6.8814862E7</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6" t="s">
+      <c r="F22" s="11">
+        <v>68814862</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A23" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="11">
-        <v>46060.0</v>
+      <c r="C23" s="10">
+        <v>46060</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E23" s="13">
-        <v>46060.78472222222</v>
-      </c>
-      <c r="F23" s="12">
-        <v>6.8763189E7</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6" t="s">
+      <c r="E23" s="8">
+        <v>46060.784722222219</v>
+      </c>
+      <c r="F23" s="11">
+        <v>68763189</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="11">
-        <v>46056.0</v>
+      <c r="C24" s="10">
+        <v>46056</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E24" s="13">
-        <v>46057.38402777778</v>
-      </c>
-      <c r="F24" s="12">
-        <v>6.8582969E7</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6" t="s">
+      <c r="E24" s="8">
+        <v>46057.384027777778</v>
+      </c>
+      <c r="F24" s="11">
+        <v>68582969</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A25" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="11">
-        <v>46056.0</v>
+      <c r="C25" s="10">
+        <v>46056</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="8">
         <v>46056.873611111114</v>
       </c>
-      <c r="F25" s="12">
-        <v>6.8612109E7</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6" t="s">
+      <c r="F25" s="11">
+        <v>68612109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="8">
-        <v>46056.0</v>
+      <c r="C26" s="7">
+        <v>46056</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="12">
         <v>46057.322916666664</v>
       </c>
-      <c r="F26" s="12">
-        <v>6.8587788E7</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6" t="s">
+      <c r="F26" s="11">
+        <v>68587788</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A27" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="8">
-        <v>46056.0</v>
+      <c r="C27" s="7">
+        <v>46056</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="12">
         <v>46056.57916666667</v>
       </c>
-      <c r="F27" s="12">
-        <v>6.8590158E7</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6" t="s">
+      <c r="F27" s="11">
+        <v>68590158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A28" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="11">
-        <v>46055.0</v>
+      <c r="C28" s="10">
+        <v>46055</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="13">
-        <v>46056.58194444444</v>
-      </c>
-      <c r="F28" s="12">
-        <v>6.8565732E7</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6" t="s">
+      <c r="E28" s="8">
+        <v>46056.581944444442</v>
+      </c>
+      <c r="F28" s="11">
+        <v>68565732</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="8">
-        <v>46054.0</v>
+      <c r="C29" s="7">
+        <v>46054</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="14">
-        <v>46055.64236111111</v>
-      </c>
-      <c r="F29" s="12">
-        <v>6.8531125E7</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6" t="s">
+      <c r="E29" s="12">
+        <v>46055.642361111109</v>
+      </c>
+      <c r="F29" s="11">
+        <v>68531125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="8">
-        <v>46053.0</v>
+      <c r="C30" s="7">
+        <v>46053</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E30" s="14">
-        <v>46056.22430555556</v>
-      </c>
-      <c r="F30" s="12">
-        <v>6.8528452E7</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6" t="s">
+      <c r="E30" s="12">
+        <v>46056.224305555559</v>
+      </c>
+      <c r="F30" s="11">
+        <v>68528452</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="11">
-        <v>46051.0</v>
+      <c r="C31" s="10">
+        <v>46051</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="8">
         <v>46051.40625</v>
       </c>
-      <c r="F31" s="12">
-        <v>6.8437375E7</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6" t="s">
+      <c r="F31" s="11">
+        <v>68437375</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="11">
-        <v>46051.0</v>
+      <c r="C32" s="10">
+        <v>46051</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E32" s="13">
-        <v>46052.22222222222</v>
-      </c>
-      <c r="F32" s="12">
-        <v>6.8439523E7</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6" t="s">
+      <c r="E32" s="8">
+        <v>46052.222222222219</v>
+      </c>
+      <c r="F32" s="11">
+        <v>68439523</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A33" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="11">
-        <v>46051.0</v>
+      <c r="C33" s="10">
+        <v>46051</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E33" s="13">
-        <v>46052.36319444444</v>
-      </c>
-      <c r="F33" s="12">
-        <v>6.8470549E7</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="6" t="s">
+      <c r="E33" s="8">
+        <v>46052.363194444442</v>
+      </c>
+      <c r="F33" s="11">
+        <v>68470549</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A34" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="8">
-        <v>46051.0</v>
+      <c r="C34" s="7">
+        <v>46051</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="14">
-        <v>46051.56805555556</v>
-      </c>
-      <c r="F34" s="12">
-        <v>6.8435815E7</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6" t="s">
+      <c r="E34" s="12">
+        <v>46051.568055555559</v>
+      </c>
+      <c r="F34" s="11">
+        <v>68435815</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="11">
-        <v>46049.0</v>
+      <c r="C35" s="10">
+        <v>46049</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="13">
-        <v>46051.34583333333</v>
-      </c>
-      <c r="F35" s="12">
-        <v>6.839324E7</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6" t="s">
+      <c r="E35" s="8">
+        <v>46051.345833333333</v>
+      </c>
+      <c r="F35" s="11">
+        <v>68393240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A36" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="8">
-        <v>46049.0</v>
+      <c r="C36" s="7">
+        <v>46049</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E36" s="12">
         <v>46050.43472222222</v>
       </c>
-      <c r="F36" s="12">
-        <v>6.838504E7</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="6" t="s">
+      <c r="F36" s="11">
+        <v>68385040</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A37" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="8">
-        <v>46049.0</v>
+      <c r="C37" s="7">
+        <v>46049</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="14">
-        <v>46050.38402777778</v>
-      </c>
-      <c r="F37" s="12">
-        <v>6.8355359E7</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6" t="s">
+      <c r="E37" s="12">
+        <v>46050.384027777778</v>
+      </c>
+      <c r="F37" s="11">
+        <v>68355359</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A38" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="8">
-        <v>46049.0</v>
+      <c r="C38" s="7">
+        <v>46049</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="12">
         <v>46050.322916666664</v>
       </c>
-      <c r="F38" s="12">
-        <v>6.8352624E7</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6" t="s">
+      <c r="F38" s="11">
+        <v>68352624</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A39" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="11">
-        <v>46048.0</v>
+      <c r="C39" s="10">
+        <v>46048</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E39" s="8">
         <v>46049.5</v>
       </c>
-      <c r="F39" s="12">
-        <v>6.831235E7</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="6" t="s">
+      <c r="F39" s="11">
+        <v>68312350</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A40" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="11">
-        <v>46048.0</v>
+      <c r="C40" s="10">
+        <v>46048</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E40" s="13">
-        <v>46049.34930555556</v>
-      </c>
-      <c r="F40" s="12">
-        <v>6.8348928E7</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="6" t="s">
+      <c r="E40" s="8">
+        <v>46049.349305555559</v>
+      </c>
+      <c r="F40" s="11">
+        <v>68348928</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A41" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="11">
-        <v>46047.0</v>
+      <c r="C41" s="10">
+        <v>46047</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E41" s="13">
+      <c r="E41" s="8">
         <v>46049.239583333336</v>
       </c>
-      <c r="F41" s="12">
-        <v>6.830871E7</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="15" t="s">
+      <c r="F41" s="11">
+        <v>68308710</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A42" s="13" t="s">
         <v>49</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C42" s="11">
-        <v>46046.0</v>
+      <c r="C42" s="10">
+        <v>46046</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E42" s="13">
-        <v>46048.56319444445</v>
-      </c>
-      <c r="F42" s="16">
-        <v>6.8297285E7</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="15" t="s">
+      <c r="E42" s="8">
+        <v>46048.563194444447</v>
+      </c>
+      <c r="F42" s="14">
+        <v>68297285</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A43" s="13" t="s">
         <v>50</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="11">
-        <v>46046.0</v>
+      <c r="C43" s="10">
+        <v>46046</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E43" s="13">
-        <v>46048.56319444445</v>
-      </c>
-      <c r="F43" s="16">
-        <v>6.8300728E7</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="15" t="s">
+      <c r="E43" s="8">
+        <v>46048.563194444447</v>
+      </c>
+      <c r="F43" s="14">
+        <v>68300728</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A44" s="13" t="s">
         <v>51</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="11">
-        <v>46046.0</v>
+      <c r="C44" s="10">
+        <v>46046</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E44" s="14">
-        <v>46046.50902777778</v>
-      </c>
-      <c r="F44" s="16">
-        <v>6.8297298E7</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="15" t="s">
+      <c r="E44" s="12">
+        <v>46046.509027777778</v>
+      </c>
+      <c r="F44" s="14">
+        <v>68297298</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A45" s="13" t="s">
         <v>52</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="11">
-        <v>46045.0</v>
+      <c r="C45" s="10">
+        <v>46045</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E45" s="14">
-        <v>46048.23402777778</v>
-      </c>
-      <c r="F45" s="16">
-        <v>6.8259856E7</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="15" t="s">
+      <c r="E45" s="12">
+        <v>46048.234027777777</v>
+      </c>
+      <c r="F45" s="14">
+        <v>68259856</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A46" s="13" t="s">
         <v>53</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C46" s="11">
-        <v>46045.0</v>
+      <c r="C46" s="10">
+        <v>46045</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E46" s="14">
-        <v>46048.30138888889</v>
-      </c>
-      <c r="F46" s="16">
-        <v>6.8283525E7</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="15" t="s">
+      <c r="E46" s="12">
+        <v>46048.301388888889</v>
+      </c>
+      <c r="F46" s="14">
+        <v>68283525</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A47" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="11">
-        <v>46045.0</v>
+      <c r="C47" s="10">
+        <v>46045</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E47" s="14">
-        <v>46045.42569444444</v>
-      </c>
-      <c r="F47" s="16">
-        <v>6.8256377E7</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="15" t="s">
+      <c r="E47" s="12">
+        <v>46045.425694444442</v>
+      </c>
+      <c r="F47" s="14">
+        <v>68256377</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A48" s="13" t="s">
         <v>55</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="11">
-        <v>46044.0</v>
+      <c r="C48" s="10">
+        <v>46044</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E48" s="14">
-        <v>46044.46944444445</v>
-      </c>
-      <c r="F48" s="16">
-        <v>6.8214612E7</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="15" t="s">
+      <c r="E48" s="12">
+        <v>46044.469444444447</v>
+      </c>
+      <c r="F48" s="14">
+        <v>68214612</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A49" s="13" t="s">
         <v>56</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="11">
-        <v>46044.0</v>
+      <c r="C49" s="10">
+        <v>46044</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="14">
-        <v>46044.46944444445</v>
-      </c>
-      <c r="F49" s="16">
-        <v>6.8215292E7</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="15" t="s">
+      <c r="E49" s="12">
+        <v>46044.469444444447</v>
+      </c>
+      <c r="F49" s="14">
+        <v>68215292</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A50" s="13" t="s">
         <v>57</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="11">
-        <v>46044.0</v>
+      <c r="C50" s="10">
+        <v>46044</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="14">
+      <c r="E50" s="12">
         <v>46044.993055555555</v>
       </c>
-      <c r="F50" s="16">
-        <v>6.8253028E7</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="17" t="s">
+      <c r="F50" s="14">
+        <v>68253028</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A51" s="13" t="s">
         <v>58</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="11">
-        <v>46043.0</v>
+      <c r="C51" s="10">
+        <v>46043</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="18">
-        <v>46044.0</v>
-      </c>
-      <c r="F51" s="17">
-        <v>6.816216E7</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="17" t="s">
+      <c r="E51" s="15">
+        <v>46044</v>
+      </c>
+      <c r="F51" s="13">
+        <v>68162160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A52" s="13" t="s">
         <v>59</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="11">
-        <v>46043.0</v>
+      <c r="C52" s="10">
+        <v>46043</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E52" s="18">
-        <v>46044.0</v>
-      </c>
-      <c r="F52" s="17">
-        <v>6.8161475E7</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="17" t="s">
+      <c r="E52" s="15">
+        <v>46044</v>
+      </c>
+      <c r="F52" s="13">
+        <v>68161475</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A53" s="13" t="s">
         <v>60</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="11">
-        <v>46043.0</v>
+      <c r="C53" s="10">
+        <v>46043</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E53" s="18">
-        <v>46043.0</v>
-      </c>
-      <c r="F53" s="17">
-        <v>6.8159581E7</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="17" t="s">
+      <c r="E53" s="15">
+        <v>46043</v>
+      </c>
+      <c r="F53" s="13">
+        <v>68159581</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A54" s="13" t="s">
         <v>61</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C54" s="11">
-        <v>46043.0</v>
+      <c r="C54" s="10">
+        <v>46043</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E54" s="18">
-        <v>46043.0</v>
-      </c>
-      <c r="F54" s="17">
-        <v>6.8096203E7</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="17" t="s">
+      <c r="E54" s="15">
+        <v>46043</v>
+      </c>
+      <c r="F54" s="13">
+        <v>68096203</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A55" s="13" t="s">
         <v>62</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="11">
-        <v>46043.0</v>
+      <c r="C55" s="10">
+        <v>46043</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E55" s="18">
-        <v>46043.0</v>
-      </c>
-      <c r="F55" s="17">
-        <v>6.8096037E7</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="17" t="s">
+      <c r="E55" s="15">
+        <v>46043</v>
+      </c>
+      <c r="F55" s="13">
+        <v>68096037</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A56" s="13" t="s">
         <v>63</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C56" s="11">
-        <v>46043.0</v>
+      <c r="C56" s="10">
+        <v>46043</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E56" s="18">
-        <v>46043.0</v>
-      </c>
-      <c r="F56" s="17">
-        <v>6.8093305E7</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="17" t="s">
+      <c r="E56" s="15">
+        <v>46043</v>
+      </c>
+      <c r="F56" s="13">
+        <v>68093305</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A57" s="13" t="s">
         <v>64</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C57" s="11">
-        <v>46043.0</v>
+      <c r="C57" s="10">
+        <v>46043</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E57" s="18">
-        <v>46043.0</v>
-      </c>
-      <c r="F57" s="17">
-        <v>6.8064468E7</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="17" t="s">
+      <c r="E57" s="15">
+        <v>46043</v>
+      </c>
+      <c r="F57" s="13">
+        <v>68064468</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A58" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="11">
-        <v>46042.0</v>
+      <c r="C58" s="10">
+        <v>46042</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E58" s="18">
-        <v>46042.0</v>
-      </c>
-      <c r="F58" s="17">
-        <v>6.8063299E7</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="17" t="s">
+      <c r="E58" s="15">
+        <v>46042</v>
+      </c>
+      <c r="F58" s="13">
+        <v>68063299</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A59" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C59" s="11">
-        <v>46042.0</v>
+      <c r="C59" s="10">
+        <v>46042</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E59" s="18">
-        <v>46042.0</v>
-      </c>
-      <c r="F59" s="17">
-        <v>6.8054062E7</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="17" t="s">
+      <c r="E59" s="15">
+        <v>46042</v>
+      </c>
+      <c r="F59" s="13">
+        <v>68054062</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A60" s="13" t="s">
         <v>67</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C60" s="11">
-        <v>46039.0</v>
+      <c r="C60" s="10">
+        <v>46039</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E60" s="18">
-        <v>46039.0</v>
-      </c>
-      <c r="F60" s="17">
-        <v>6.808527E7</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="17" t="s">
+      <c r="E60" s="15">
+        <v>46039</v>
+      </c>
+      <c r="F60" s="13">
+        <v>68085270</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A61" s="13" t="s">
         <v>68</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C61" s="11">
-        <v>46039.0</v>
+      <c r="C61" s="10">
+        <v>46039</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E61" s="18">
-        <v>46039.0</v>
-      </c>
-      <c r="F61" s="17">
-        <v>6.806019E7</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="17" t="s">
+      <c r="E61" s="15">
+        <v>46039</v>
+      </c>
+      <c r="F61" s="13">
+        <v>68060190</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A62" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C62" s="11">
-        <v>46038.0</v>
+      <c r="C62" s="10">
+        <v>46038</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E62" s="18">
-        <v>46038.0</v>
-      </c>
-      <c r="F62" s="17">
-        <v>6.8055033E7</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="17" t="s">
+      <c r="E62" s="15">
+        <v>46038</v>
+      </c>
+      <c r="F62" s="13">
+        <v>68055033</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A63" s="13" t="s">
         <v>70</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C63" s="11">
-        <v>46038.0</v>
+      <c r="C63" s="10">
+        <v>46038</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E63" s="18">
-        <v>46038.0</v>
-      </c>
-      <c r="F63" s="17">
-        <v>6.800621E7</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="17" t="s">
+      <c r="E63" s="15">
+        <v>46038</v>
+      </c>
+      <c r="F63" s="13">
+        <v>68006210</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A64" s="13" t="s">
         <v>71</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C64" s="18">
-        <v>46037.0</v>
+      <c r="C64" s="15">
+        <v>46037</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E64" s="18">
-        <v>46037.0</v>
-      </c>
-      <c r="F64" s="17">
-        <v>6.8004416E7</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="17" t="s">
+      <c r="E64" s="15">
+        <v>46037</v>
+      </c>
+      <c r="F64" s="13">
+        <v>68004416</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A65" s="13" t="s">
         <v>72</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C65" s="18">
-        <v>46036.0</v>
+      <c r="C65" s="15">
+        <v>46036</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E65" s="18">
-        <v>46036.0</v>
-      </c>
-      <c r="F65" s="17">
-        <v>6.7884884E7</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="17" t="s">
+      <c r="E65" s="15">
+        <v>46036</v>
+      </c>
+      <c r="F65" s="13">
+        <v>67884884</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A66" s="13" t="s">
         <v>73</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C66" s="18">
-        <v>46034.0</v>
+      <c r="C66" s="15">
+        <v>46034</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E66" s="18">
-        <v>46034.0</v>
-      </c>
-      <c r="F66" s="17">
-        <v>6.7859093E7</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="17" t="s">
+      <c r="E66" s="15">
+        <v>46034</v>
+      </c>
+      <c r="F66" s="13">
+        <v>67859093</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A67" s="13" t="s">
         <v>74</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="18">
-        <v>46032.0</v>
+      <c r="C67" s="15">
+        <v>46032</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E67" s="18">
-        <v>46032.0</v>
-      </c>
-      <c r="F67" s="17">
-        <v>6.7849285E7</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="17" t="s">
+      <c r="E67" s="15">
+        <v>46032</v>
+      </c>
+      <c r="F67" s="13">
+        <v>67849285</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A68" s="13" t="s">
         <v>75</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C68" s="18">
-        <v>46031.0</v>
+      <c r="C68" s="15">
+        <v>46031</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E68" s="18">
-        <v>46031.0</v>
-      </c>
-      <c r="F68" s="17">
-        <v>6.7762628E7</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="17" t="s">
+      <c r="E68" s="15">
+        <v>46031</v>
+      </c>
+      <c r="F68" s="13">
+        <v>67762628</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A69" s="13" t="s">
         <v>76</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C69" s="18">
-        <v>46031.0</v>
+      <c r="C69" s="15">
+        <v>46031</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E69" s="18">
-        <v>46031.0</v>
-      </c>
-      <c r="F69" s="17">
-        <v>6.7759103E7</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="17" t="s">
+      <c r="E69" s="15">
+        <v>46031</v>
+      </c>
+      <c r="F69" s="13">
+        <v>67759103</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A70" s="13" t="s">
         <v>77</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C70" s="18">
-        <v>46030.0</v>
+      <c r="C70" s="15">
+        <v>46030</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E70" s="18">
-        <v>46030.0</v>
-      </c>
-      <c r="F70" s="17">
-        <v>6.7762831E7</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="17" t="s">
+      <c r="E70" s="15">
+        <v>46030</v>
+      </c>
+      <c r="F70" s="13">
+        <v>67762831</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A71" s="13" t="s">
         <v>78</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C71" s="18">
-        <v>46029.0</v>
+      <c r="C71" s="15">
+        <v>46029</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E71" s="18">
-        <v>46029.0</v>
-      </c>
-      <c r="F71" s="17">
-        <v>6.7721974E7</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="17" t="s">
+      <c r="E71" s="15">
+        <v>46029</v>
+      </c>
+      <c r="F71" s="13">
+        <v>67721974</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A72" s="13" t="s">
         <v>79</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C72" s="18">
-        <v>46029.0</v>
+      <c r="C72" s="15">
+        <v>46029</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E72" s="18">
-        <v>46029.0</v>
-      </c>
-      <c r="F72" s="17">
-        <v>6.7715206E7</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="17" t="s">
+      <c r="E72" s="15">
+        <v>46029</v>
+      </c>
+      <c r="F72" s="13">
+        <v>67715206</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A73" s="13" t="s">
         <v>80</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="18">
-        <v>46029.0</v>
+      <c r="C73" s="15">
+        <v>46029</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E73" s="18">
-        <v>46029.0</v>
-      </c>
-      <c r="F73" s="17">
-        <v>6.7697497E7</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="17" t="s">
+      <c r="E73" s="15">
+        <v>46029</v>
+      </c>
+      <c r="F73" s="13">
+        <v>67697497</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A74" s="13" t="s">
         <v>81</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C74" s="18">
-        <v>46027.0</v>
+      <c r="C74" s="15">
+        <v>46027</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E74" s="18">
-        <v>46027.0</v>
-      </c>
-      <c r="F74" s="17">
-        <v>6.7625691E7</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="17" t="s">
+      <c r="E74" s="15">
+        <v>46027</v>
+      </c>
+      <c r="F74" s="13">
+        <v>67625691</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A75" s="13" t="s">
         <v>82</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C75" s="18">
-        <v>46027.0</v>
+      <c r="C75" s="15">
+        <v>46027</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E75" s="18">
-        <v>46027.0</v>
-      </c>
-      <c r="F75" s="17">
-        <v>6.7625263E7</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="17" t="s">
+      <c r="E75" s="15">
+        <v>46027</v>
+      </c>
+      <c r="F75" s="13">
+        <v>67625263</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A76" s="13" t="s">
         <v>83</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C76" s="18">
-        <v>46027.0</v>
+      <c r="C76" s="15">
+        <v>46027</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E76" s="18">
-        <v>46027.0</v>
-      </c>
-      <c r="F76" s="17">
-        <v>6.7517577E7</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="17" t="s">
+      <c r="E76" s="15">
+        <v>46027</v>
+      </c>
+      <c r="F76" s="13">
+        <v>67517577</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A77" s="13" t="s">
         <v>84</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C77" s="18">
-        <v>46024.0</v>
+      <c r="C77" s="15">
+        <v>46024</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E77" s="18">
-        <v>46024.0</v>
-      </c>
-      <c r="F77" s="17">
-        <v>6.7585753E7</v>
-      </c>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="17" t="s">
+      <c r="E77" s="15">
+        <v>46024</v>
+      </c>
+      <c r="F77" s="13">
+        <v>67585753</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A78" s="13" t="s">
         <v>85</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C78" s="18">
-        <v>46022.0</v>
+      <c r="C78" s="15">
+        <v>46022</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E78" s="18">
-        <v>46022.0</v>
-      </c>
-      <c r="F78" s="17">
-        <v>6.7565928E7</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="17" t="s">
+      <c r="E78" s="15">
+        <v>46022</v>
+      </c>
+      <c r="F78" s="13">
+        <v>67565928</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A79" s="13" t="s">
         <v>86</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C79" s="18">
-        <v>46021.0</v>
+      <c r="C79" s="15">
+        <v>46021</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E79" s="18">
-        <v>46021.0</v>
-      </c>
-      <c r="F79" s="17">
-        <v>6.7517959E7</v>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="17" t="s">
+      <c r="E79" s="15">
+        <v>46021</v>
+      </c>
+      <c r="F79" s="13">
+        <v>67517959</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A80" s="13" t="s">
         <v>87</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C80" s="18">
-        <v>46021.0</v>
+      <c r="C80" s="15">
+        <v>46021</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E80" s="18">
-        <v>46021.0</v>
-      </c>
-      <c r="F80" s="17">
-        <v>6.7516265E7</v>
-      </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="17" t="s">
+      <c r="E80" s="15">
+        <v>46021</v>
+      </c>
+      <c r="F80" s="13">
+        <v>67516265</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A81" s="13" t="s">
         <v>88</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C81" s="18">
-        <v>46021.0</v>
+      <c r="C81" s="15">
+        <v>46021</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E81" s="18">
-        <v>46021.0</v>
-      </c>
-      <c r="F81" s="17">
-        <v>6.7513322E7</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="17" t="s">
+      <c r="E81" s="15">
+        <v>46021</v>
+      </c>
+      <c r="F81" s="13">
+        <v>67513322</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A82" s="13" t="s">
         <v>89</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C82" s="18">
-        <v>46020.0</v>
+      <c r="C82" s="15">
+        <v>46020</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E82" s="18">
-        <v>46020.0</v>
-      </c>
-      <c r="F82" s="17">
-        <v>6.7471786E7</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="17" t="s">
+      <c r="E82" s="15">
+        <v>46020</v>
+      </c>
+      <c r="F82" s="13">
+        <v>67471786</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A83" s="13" t="s">
         <v>90</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C83" s="18">
-        <v>46017.0</v>
+      <c r="C83" s="15">
+        <v>46017</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E83" s="18">
-        <v>46017.0</v>
-      </c>
-      <c r="F83" s="17">
-        <v>6.7429778E7</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="17" t="s">
+      <c r="E83" s="15">
+        <v>46017</v>
+      </c>
+      <c r="F83" s="13">
+        <v>67429778</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A84" s="13" t="s">
         <v>91</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C84" s="18">
-        <v>46013.0</v>
+      <c r="C84" s="15">
+        <v>46013</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E84" s="18">
-        <v>46013.0</v>
-      </c>
-      <c r="F84" s="17">
-        <v>6.7346647E7</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
+      <c r="E84" s="15">
+        <v>46013</v>
+      </c>
+      <c r="F84" s="13">
+        <v>67346647</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="86" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="87" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="88" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="89" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="90" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="91" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="92" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="93" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="94" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="95" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="96" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1"/>
     <row r="99" ht="15.75" customHeight="1"/>
@@ -3145,9 +3165,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>